--- a/artfynd/A 38741-2026 artfynd.xlsx
+++ b/artfynd/A 38741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583106</v>
       </c>
       <c r="B2" t="n">
-        <v>101580</v>
+        <v>101582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136583103</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583102</v>
       </c>
       <c r="B5" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136583107</v>
       </c>
       <c r="B9" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38741-2026 artfynd.xlsx
+++ b/artfynd/A 38741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583106</v>
       </c>
       <c r="B2" t="n">
-        <v>101582</v>
+        <v>101588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136583108</v>
       </c>
       <c r="B3" t="n">
-        <v>80592</v>
+        <v>80596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136583103</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583102</v>
       </c>
       <c r="B5" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136583111</v>
       </c>
       <c r="B6" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136583105</v>
       </c>
       <c r="B7" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136583109</v>
       </c>
       <c r="B8" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136583107</v>
       </c>
       <c r="B9" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136583110</v>
       </c>
       <c r="B10" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136583104</v>
       </c>
       <c r="B11" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 38741-2026 artfynd.xlsx
+++ b/artfynd/A 38741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583106</v>
       </c>
       <c r="B2" t="n">
-        <v>101588</v>
+        <v>101590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136583108</v>
       </c>
       <c r="B3" t="n">
-        <v>80596</v>
+        <v>80598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136583103</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583102</v>
       </c>
       <c r="B5" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136583111</v>
       </c>
       <c r="B6" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136583105</v>
       </c>
       <c r="B7" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136583109</v>
       </c>
       <c r="B8" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136583107</v>
       </c>
       <c r="B9" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136583110</v>
       </c>
       <c r="B10" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136583104</v>
       </c>
       <c r="B11" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 38741-2026 artfynd.xlsx
+++ b/artfynd/A 38741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583106</v>
       </c>
       <c r="B2" t="n">
-        <v>101590</v>
+        <v>101591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136583108</v>
       </c>
       <c r="B3" t="n">
-        <v>80598</v>
+        <v>80599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136583103</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583102</v>
       </c>
       <c r="B5" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136583111</v>
       </c>
       <c r="B6" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136583105</v>
       </c>
       <c r="B7" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136583109</v>
       </c>
       <c r="B8" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136583107</v>
       </c>
       <c r="B9" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136583110</v>
       </c>
       <c r="B10" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136583104</v>
       </c>
       <c r="B11" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 38741-2026 artfynd.xlsx
+++ b/artfynd/A 38741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583106</v>
       </c>
       <c r="B2" t="n">
-        <v>101591</v>
+        <v>101597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136583103</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583102</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136583107</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38741-2026 artfynd.xlsx
+++ b/artfynd/A 38741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583106</v>
       </c>
       <c r="B2" t="n">
-        <v>101597</v>
+        <v>101601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136583108</v>
       </c>
       <c r="B3" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136583103</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583102</v>
       </c>
       <c r="B5" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136583111</v>
       </c>
       <c r="B6" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136583105</v>
       </c>
       <c r="B7" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136583109</v>
       </c>
       <c r="B8" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136583107</v>
       </c>
       <c r="B9" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136583110</v>
       </c>
       <c r="B10" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136583104</v>
       </c>
       <c r="B11" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 38741-2026 artfynd.xlsx
+++ b/artfynd/A 38741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583106</v>
       </c>
       <c r="B2" t="n">
-        <v>101601</v>
+        <v>101603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136583107</v>
       </c>
       <c r="B9" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38741-2026 artfynd.xlsx
+++ b/artfynd/A 38741-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583106</v>
       </c>
       <c r="B2" t="n">
-        <v>101603</v>
+        <v>101605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136583108</v>
       </c>
       <c r="B3" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136583103</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>136583102</v>
       </c>
       <c r="B5" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>136583111</v>
       </c>
       <c r="B6" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136583105</v>
       </c>
       <c r="B7" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>136583109</v>
       </c>
       <c r="B8" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>136583107</v>
       </c>
       <c r="B9" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>136583110</v>
       </c>
       <c r="B10" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>136583104</v>
       </c>
       <c r="B11" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
